--- a/docs/SchoolGrid_导入数据.xlsx
+++ b/docs/SchoolGrid_导入数据.xlsx
@@ -1,11 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet name="排课名单" sheetId="1" r:id="rId1"/>
-    <sheet name="阅读说明" sheetId="2" r:id="rId2"/>
+    <sheet name="排课名单" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="阅读说明" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
+  <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
@@ -31,17 +38,294 @@
 </metadata>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+  <si>
+    <t>年级</t>
+  </si>
+  <si>
+    <t>班级名称</t>
+  </si>
+  <si>
+    <t>班主任</t>
+  </si>
+  <si>
+    <t>语文</t>
+  </si>
+  <si>
+    <t>数学</t>
+  </si>
+  <si>
+    <t>英语</t>
+  </si>
+  <si>
+    <t>政治</t>
+  </si>
+  <si>
+    <t>历史</t>
+  </si>
+  <si>
+    <t>地理</t>
+  </si>
+  <si>
+    <t>物理</t>
+  </si>
+  <si>
+    <t>生物</t>
+  </si>
+  <si>
+    <t>艺术1</t>
+  </si>
+  <si>
+    <t>艺术2</t>
+  </si>
+  <si>
+    <t>劳动</t>
+  </si>
+  <si>
+    <t>体育</t>
+  </si>
+  <si>
+    <t>初二</t>
+  </si>
+  <si>
+    <t>初二（1）班</t>
+  </si>
+  <si>
+    <t>李明轩</t>
+  </si>
+  <si>
+    <t>王雅静</t>
+  </si>
+  <si>
+    <t>杨帆</t>
+  </si>
+  <si>
+    <t>高远</t>
+  </si>
+  <si>
+    <t>唐磊</t>
+  </si>
+  <si>
+    <t xml:space="preserve">程琳 </t>
+  </si>
+  <si>
+    <t>许晨曦</t>
+  </si>
+  <si>
+    <t>蔡明</t>
+  </si>
+  <si>
+    <t>曹宇</t>
+  </si>
+  <si>
+    <t>沈力</t>
+  </si>
+  <si>
+    <t>江雪</t>
+  </si>
+  <si>
+    <t>方文</t>
+  </si>
+  <si>
+    <t>初二（2）班</t>
+  </si>
+  <si>
+    <t>初二（3）班</t>
+  </si>
+  <si>
+    <t>张浩然</t>
+  </si>
+  <si>
+    <t>陈思琪</t>
+  </si>
+  <si>
+    <t>徐海燕</t>
+  </si>
+  <si>
+    <t>初二（4）班</t>
+  </si>
+  <si>
+    <t>罗嘉欣</t>
+  </si>
+  <si>
+    <t>潘峰</t>
+  </si>
+  <si>
+    <t>初二（5）班</t>
+  </si>
+  <si>
+    <t>刘建华</t>
+  </si>
+  <si>
+    <t>赵梦瑶</t>
+  </si>
+  <si>
+    <t>马晓东</t>
+  </si>
+  <si>
+    <t>韩雪梅</t>
+  </si>
+  <si>
+    <t>邓晓华</t>
+  </si>
+  <si>
+    <t>初二（6）班</t>
+  </si>
+  <si>
+    <t>初二（7）班</t>
+  </si>
+  <si>
+    <t>孙天宇</t>
+  </si>
+  <si>
+    <t>周雨欣</t>
+  </si>
+  <si>
+    <t>林诗韵</t>
+  </si>
+  <si>
+    <t>谢文杰</t>
+  </si>
+  <si>
+    <t>梁伟</t>
+  </si>
+  <si>
+    <t>蒋欣</t>
+  </si>
+  <si>
+    <t>彭丽</t>
+  </si>
+  <si>
+    <t>苏敏</t>
+  </si>
+  <si>
+    <t>董静</t>
+  </si>
+  <si>
+    <t xml:space="preserve">邹欣 </t>
+  </si>
+  <si>
+    <t>初二（8）班</t>
+  </si>
+  <si>
+    <t>初二（9）班</t>
+  </si>
+  <si>
+    <t>吴文博</t>
+  </si>
+  <si>
+    <t>郑晓峰</t>
+  </si>
+  <si>
+    <t>郭子墨 </t>
+  </si>
+  <si>
+    <t>董泽</t>
+  </si>
+  <si>
+    <t>韩冰</t>
+  </si>
+  <si>
+    <t>初二（10）班</t>
+  </si>
+  <si>
+    <t xml:space="preserve">郭子墨 </t>
+  </si>
+  <si>
+    <t>宋佳音</t>
+  </si>
+  <si>
+    <t>夏雨</t>
+  </si>
+  <si>
+    <t>初二（11）班</t>
+  </si>
+  <si>
+    <t>冯雅琴</t>
+  </si>
+  <si>
+    <t>朱志远</t>
+  </si>
+  <si>
+    <t>何静怡</t>
+  </si>
+  <si>
+    <t>初二（12）班</t>
+  </si>
+  <si>
+    <t>数据导入超简明说明</t>
+  </si>
+  <si>
+    <t>只需填写一张表格，无需复制黏贴各种长代码！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 班级标识：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - 每一行代表一个班级，年级（如：高一）和班级名称（如：高一2班）必填。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. 谁教谁（任课关系）：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - 从第四列起是所有的学科名字。你可以自由增减列数，但请确保表头名是标准学科名称（如：语文、数学、地理等）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - 在这一列，属于这个班的单元格处，填上任课老师的姓名。如果有同名老师，请加上后缀（如：李四大、李四小）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. 排课规则去哪里配置：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - 本表极其纯净，因为所有复杂的【排几节课】、【连堂】和【禁排时间】不再需要填写在 Excel 内。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - 等导入本文件成功后，进入界面菜单的「排课规则」页面直接设置。系统会自动将名单和规则合成处理。</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7">
     <font>
-      <sz val="12"/>
+      <sz val="12.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <color indexed="64"/>
+      <name val="Helvetica Neue"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <color indexed="64"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <color indexed="64"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14.500000"/>
+      <color indexed="64"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="8.500000"/>
+      <color indexed="64"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="8.500000"/>
+      <color indexed="64"/>
+      <name val="Helvetica Neue"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -55,28 +339,52 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="10">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -122,13 +430,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -151,19 +459,18 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -186,7 +493,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -221,16 +527,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -352,9 +662,226 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -373,7 +900,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -392,176 +919,766 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10.83203125"/>
+    <col customWidth="1" min="2" max="2" width="15.83203125"/>
+    <col customWidth="1" min="3" max="3" width="12.83203125"/>
+    <col customWidth="1" min="4" max="12" width="10.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>年级</v>
-      </c>
-      <c r="B1" t="str">
-        <v>班级名称</v>
-      </c>
-      <c r="C1" t="str">
-        <v>班主任</v>
-      </c>
-      <c r="D1" t="str">
-        <v>语文</v>
-      </c>
-      <c r="E1" t="str">
-        <v>数学</v>
-      </c>
-      <c r="F1" t="str">
-        <v>英语</v>
-      </c>
-      <c r="G1" t="str">
-        <v>物理</v>
-      </c>
-      <c r="H1" t="str">
-        <v>历史</v>
-      </c>
-      <c r="I1" t="str">
-        <v>音乐</v>
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>高一</v>
-      </c>
-      <c r="B2" t="str">
-        <v>高一1班</v>
-      </c>
-      <c r="C2" t="str">
-        <v>张老实</v>
-      </c>
-      <c r="D2" t="str">
-        <v>王文学</v>
-      </c>
-      <c r="E2" t="str">
-        <v>张算数</v>
-      </c>
-      <c r="F2" t="str">
-        <v>李外语</v>
-      </c>
-      <c r="G2" t="str">
-        <v>赵牛顿</v>
-      </c>
-      <c r="H2" t="str">
-        <v>钱史记</v>
-      </c>
-      <c r="I2" t="str">
-        <v>周贝多</v>
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>高一</v>
-      </c>
-      <c r="B3" t="str">
-        <v>高一2班</v>
-      </c>
-      <c r="C3" t="str">
-        <v>王文学</v>
-      </c>
-      <c r="D3" t="str">
-        <v>吴作文</v>
-      </c>
-      <c r="E3" t="str">
-        <v>张算数</v>
-      </c>
-      <c r="F3" t="str">
-        <v>郑语法</v>
-      </c>
-      <c r="G3" t="str">
-        <v>孙阿基</v>
-      </c>
-      <c r="H3" t="str">
-        <v>钱史记</v>
-      </c>
-      <c r="I3" t="str">
-        <v>周贝多</v>
-      </c>
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" t="s">
+        <v>52</v>
+      </c>
+      <c r="N8" t="s">
+        <v>53</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M10" t="s">
+        <v>52</v>
+      </c>
+      <c r="N10" t="s">
+        <v>53</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5">
+      <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M11" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" t="s">
+        <v>53</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5">
+      <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" t="s">
+        <v>51</v>
+      </c>
+      <c r="M12" t="s">
+        <v>52</v>
+      </c>
+      <c r="N12" t="s">
+        <v>53</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5">
+      <c r="A13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" t="s">
+        <v>51</v>
+      </c>
+      <c r="M13" t="s">
+        <v>52</v>
+      </c>
+      <c r="N13" t="s">
+        <v>53</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5">
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" ht="16.5">
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" ht="18">
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" ht="16.5">
+      <c r="C17" s="8"/>
+    </row>
+    <row r="18" ht="16.5">
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" ht="16.5">
+      <c r="C19" s="6"/>
+    </row>
+    <row r="20" ht="16.5">
+      <c r="C20" s="6"/>
+    </row>
+    <row r="21" ht="16.5">
+      <c r="C21" s="6"/>
+    </row>
+    <row r="22" ht="16.5">
+      <c r="C22" s="6"/>
+    </row>
+    <row r="23" ht="16.5">
+      <c r="C23" s="6"/>
+      <c r="D23" s="9"/>
+    </row>
+    <row r="24" ht="16.5">
+      <c r="C24" s="6"/>
+      <c r="D24" s="9"/>
+    </row>
+    <row r="25" ht="16.5">
+      <c r="C25" s="6"/>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" ht="16.5">
+      <c r="C26" s="6"/>
+      <c r="D26" s="9"/>
+    </row>
+    <row r="27" ht="16.5">
+      <c r="C27" s="6"/>
+      <c r="D27" s="9"/>
+    </row>
+    <row r="28" ht="16.5">
+      <c r="C28" s="6"/>
+      <c r="D28" s="9"/>
+    </row>
+    <row r="29" ht="16.5">
+      <c r="C29" s="6"/>
+      <c r="D29" s="9"/>
+    </row>
+    <row r="30" ht="16.5">
+      <c r="D30" s="9"/>
+    </row>
+    <row r="31" ht="16.5">
+      <c r="D31" s="9"/>
+    </row>
+    <row r="32" ht="16.5">
+      <c r="D32" s="9"/>
+    </row>
+    <row r="33" ht="16.5">
+      <c r="D33" s="9"/>
+    </row>
+    <row r="34" ht="16.5">
+      <c r="D34" s="9"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
-  </ignoredErrors>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>数据导入超简明说明</v>
+      <c r="A1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>只需填写一张表格，无需复制黏贴各种长代码！</v>
+      <c r="A3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>1. 班级标识：</v>
+      <c r="A5" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v xml:space="preserve">   - 每一行代表一个班级，年级（如：高一）和班级名称（如：高一2班）必填。</v>
+      <c r="A6" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>2. 谁教谁（任课关系）：</v>
+      <c r="A8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v xml:space="preserve">   - 从第四列起是所有的学科名字。你可以自由增减列数，但请确保表头名是标准学科名称（如：语文、数学、地理等）。</v>
+      <c r="A9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v xml:space="preserve">   - 在这一列，属于这个班的单元格处，填上任课老师的姓名。如果有同名老师，请加上后缀（如：李四大、李四小）。</v>
+      <c r="A10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>3. 排课规则去哪里配置：</v>
+      <c r="A12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v xml:space="preserve">   - 本表极其纯净，因为所有复杂的【排几节课】、【连堂】和【禁排时间】不再需要填写在 Excel 内。</v>
+      <c r="A13" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v xml:space="preserve">   - 等导入本文件成功后，进入界面菜单的「排课规则」页面直接设置。系统会自动将名单和规则合成处理。</v>
+      <c r="A14" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A14"/>
-  </ignoredErrors>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>